--- a/artfynd/A 20935-2023 artfynd.xlsx
+++ b/artfynd/A 20935-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109824240</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828969</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109823055</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109824277</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109824134</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828500</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109822429</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109825274</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109826438</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109826982</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1750,6 +1805,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109827175</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109829072</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109825880</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109829283</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109822299</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2240,6 +2320,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109822364</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2338,6 +2423,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109822551</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2436,6 +2526,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109822811</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2534,6 +2629,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109822958</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2632,6 +2732,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109823202</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2730,6 +2835,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109824043</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2828,6 +2938,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109824259</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2926,6 +3041,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109824800</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3024,6 +3144,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109824849</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3122,6 +3247,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109825095</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3220,6 +3350,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109825276</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3318,6 +3453,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109825885</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3416,6 +3556,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109826864</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3514,6 +3659,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109827133</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3612,6 +3762,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828315</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3710,6 +3865,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828435</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3808,6 +3968,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828542</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3906,6 +4071,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828708</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4004,6 +4174,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109829005</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4102,6 +4277,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109829130</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4200,6 +4380,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109829209</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4298,6 +4483,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109829296</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4396,6 +4586,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109829403</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4494,6 +4689,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109829574</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4592,6 +4792,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109829632</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4690,6 +4895,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109822367</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4788,6 +4998,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109822787</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4886,6 +5101,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109824009</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4984,6 +5204,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109824786</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5082,6 +5307,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109824952</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5180,6 +5410,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109825090</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5278,6 +5513,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109825344</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5376,6 +5616,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109825882</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5474,6 +5719,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109826551</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5572,6 +5822,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828612</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5670,6 +5925,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109829073</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5768,6 +6028,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109829245</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5866,6 +6131,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109829431</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5964,6 +6234,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109829552</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6062,6 +6337,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828680</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6160,6 +6440,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828676</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6263,6 +6548,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109822445</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6366,6 +6656,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109823919</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6469,6 +6764,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109826130</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6572,6 +6872,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109826269</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6675,6 +6980,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109826897</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6778,6 +7088,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109827024</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6881,6 +7196,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109827391</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6979,8 +7299,79 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109828235</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>